--- a/HSK1_parts_of_speech_9(401-450).xlsx
+++ b/HSK1_parts_of_speech_9(401-450).xlsx
@@ -601,6 +601,21 @@
           <t>маленький</t>
         </is>
       </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>мелочь (大小)</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>маленький, небольшой</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>малый (小儿子 — младший сын)</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -627,6 +642,11 @@
           <t>ребёнок</t>
         </is>
       </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>ребёнок, малыш</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -653,6 +673,11 @@
           <t>девушка (обращение)</t>
         </is>
       </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>девушка (вежливое обращение)</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -679,6 +704,11 @@
           <t>ребёнок; малыш (обращение)</t>
         </is>
       </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>ребёнок, малыш (ласковое обращение)</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -705,6 +735,16 @@
           <t>час</t>
         </is>
       </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>час (единица времени)</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>для часов (一个小时)</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -731,6 +771,11 @@
           <t>начальная школа</t>
         </is>
       </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>начальная школа</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -757,6 +802,11 @@
           <t>ученик начальной школы</t>
         </is>
       </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>ученик начальной школы</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -783,6 +833,16 @@
           <t>смеяться, смех</t>
         </is>
       </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>смех, улыбка (笑脸)</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>смеяться, улыбаться</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -809,6 +869,11 @@
           <t>писать</t>
         </is>
       </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>писать; рисовать (写字)</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -835,6 +900,21 @@
           <t>спасибо</t>
         </is>
       </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>благодарить (谢谢你)</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>спасибо!</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>устойчивое выражение вежливости (междометие/глагол)</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -861,6 +941,16 @@
           <t>новый</t>
         </is>
       </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>новый</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>вновь (新来的人 — новоприбывший)</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -887,6 +977,11 @@
           <t>Новый год</t>
         </is>
       </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Новый год</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -913,6 +1008,11 @@
           <t>неделя</t>
         </is>
       </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>неделя (星期 + день недели)</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -939,6 +1039,11 @@
           <t>воскресенье</t>
         </is>
       </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>воскресенье</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -965,6 +1070,11 @@
           <t>воскресенье</t>
         </is>
       </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>воскресенье (разг.)</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -991,6 +1101,26 @@
           <t>можно; хорошо, пойдёт</t>
         </is>
       </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>подходить, годиться</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>сойдёт, нормально</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>достаточно (不行 — нельзя)</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>ладно!, идёт!</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -1017,6 +1147,21 @@
           <t>отдыхать</t>
         </is>
       </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>отдых (休息时间)</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>отдыхать</t>
+        </is>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>离合词: разнимается — 休息了一下</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -1043,6 +1188,21 @@
           <t>учить, учиться</t>
         </is>
       </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>учение, знание (问学问 — спрашивать о знаниях)</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>учить, учиться</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>учебный (在 составных: 学费 — плата за обучение)</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -1069,6 +1229,11 @@
           <t>ученик</t>
         </is>
       </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>ученик, студент</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -1095,6 +1260,21 @@
           <t>учиться</t>
         </is>
       </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>учёба, обучение</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>учиться, изучать</t>
+        </is>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>离合词: 学习了一天中文</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -1121,6 +1301,11 @@
           <t>школа</t>
         </is>
       </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>школа</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -1147,6 +1332,11 @@
           <t>институт</t>
         </is>
       </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>институт, факультет</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -1173,6 +1363,16 @@
           <t>хотеть, надо</t>
         </is>
       </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>хотеть; нужно, надо</t>
+        </is>
+      </c>
+      <c r="Q24" t="inlineStr">
+        <is>
+          <t>буду (составное сказуемое: 要去 — собираться пойти)</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -1199,6 +1399,11 @@
           <t>дедушка (со стороны отца)</t>
         </is>
       </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>дедушка (по отцовской линии)</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -1225,6 +1430,11 @@
           <t>тоже</t>
         </is>
       </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>тоже, также</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -1251,6 +1461,16 @@
           <t>страница</t>
         </is>
       </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>страница</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>для страниц книг и журналов (一页纸)</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -1277,6 +1497,16 @@
           <t>один</t>
         </is>
       </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>один</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>весь, целиком (一 + V: 一看就知道 — стоит посмотреть, сразу понятно)</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -1303,6 +1533,11 @@
           <t>одежда</t>
         </is>
       </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>одежда</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -1329,6 +1564,11 @@
           <t>врач</t>
         </is>
       </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>врач, доктор</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -1355,6 +1595,11 @@
           <t>больница</t>
         </is>
       </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>больница</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -1381,6 +1626,21 @@
           <t>половина</t>
         </is>
       </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>половина</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>половина (一半的人)</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>половина (吃了一半 — съел половину)</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -1407,6 +1667,26 @@
           <t>вскоре</t>
         </is>
       </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>короткое время</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>через некоторое время (一会儿见 — увидимся чуть позже)</t>
+        </is>
+      </c>
+      <c r="Q33" t="inlineStr">
+        <is>
+          <t>скоро, через минутку</t>
+        </is>
+      </c>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>грамматическая конструкция времени с редупликацией (一会儿…一会儿…)</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -1433,6 +1713,21 @@
           <t>вместе</t>
         </is>
       </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>кусок, глыба (в составе 一块儿 — вместе)</t>
+        </is>
+      </c>
+      <c r="Q34" t="inlineStr">
+        <is>
+          <t>вместе</t>
+        </is>
+      </c>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>наречие образовано от счётного слова 块儿 + 儿</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -1459,6 +1754,21 @@
           <t>сразу; разок</t>
         </is>
       </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>разок, немного (看一下儿 — взглянуть разок)</t>
+        </is>
+      </c>
+      <c r="Q35" t="inlineStr">
+        <is>
+          <t>на секунду, быстро</t>
+        </is>
+      </c>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>кратковременное дополнение при глаголе (V + 一下儿)</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -1485,6 +1795,21 @@
           <t>одинаково</t>
         </is>
       </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>одинаковый, такой же</t>
+        </is>
+      </c>
+      <c r="Q36" t="inlineStr">
+        <is>
+          <t>одинаково (长得一样 — выглядят одинаково)</t>
+        </is>
+      </c>
+      <c r="X36" t="inlineStr">
+        <is>
+          <t>устойчивое сравнительное сочетание</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -1511,6 +1836,26 @@
           <t>одна сторона</t>
         </is>
       </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>сторона, бок</t>
+        </is>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>для сторон/берегов (一边脸 — одна сторона лица; 河的一边 — берег реки)</t>
+        </is>
+      </c>
+      <c r="Q37" t="inlineStr">
+        <is>
+          <t>в то время как (一边…一边… — делая и то и другое одновременно)</t>
+        </is>
+      </c>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>в значении «делая…» — грамматизованная конструкция</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -1537,6 +1882,21 @@
           <t>немного</t>
         </is>
       </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>капелька, чуть-чуть</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>немного (一点儿水)</t>
+        </is>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>немного, чуточку (好一点儿 — получше)</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -1563,6 +1923,11 @@
           <t>вместе</t>
         </is>
       </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>вместе, совместно</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -1589,6 +1954,16 @@
           <t>немного</t>
         </is>
       </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>несколько, немного (一些人 — несколько человек)</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>кое-какие, некоторые</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -1615,6 +1990,16 @@
           <t>использовать</t>
         </is>
       </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>использовать, применять</t>
+        </is>
+      </c>
+      <c r="R41" t="inlineStr">
+        <is>
+          <t>посредством, при помощи (用汉语说 — сказать по-китайски)</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -1641,6 +2026,11 @@
           <t>иметь</t>
         </is>
       </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>иметь, обладать; существоваться (有…的)</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -1667,6 +2057,21 @@
           <t>имеющийся; некоторые</t>
         </is>
       </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>некоторые, кое-кто (有的…有的… — одни…, другие…)</t>
+        </is>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>субстантивация: 有 + частица 的</t>
+        </is>
+      </c>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>грамматическая конструкция: 有的 + существительное/предложение</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -1693,6 +2098,11 @@
           <t>известный</t>
         </is>
       </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>известный, знаменитый</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -1724,6 +2134,16 @@
           <t>иногда</t>
         </is>
       </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>иногда (= 有时候)</t>
+        </is>
+      </c>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>наречие времени (有时候…有时候…)</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -1755,6 +2175,16 @@
           <t>некоторые, несколько</t>
         </is>
       </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>немного, несколько (有一些 — есть немного)</t>
+        </is>
+      </c>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>вариант использования 有 + 一些</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -1781,6 +2211,21 @@
           <t>полезный</t>
         </is>
       </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>польза (没有用 — бесполезно)</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>пригодиться</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>полезный</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -1807,6 +2252,21 @@
           <t>правый</t>
         </is>
       </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>правая сторона</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>правый</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>правый (右手 — правая рука)</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -1833,6 +2293,11 @@
           <t>справа, правая сторона</t>
         </is>
       </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>правая сторона, справа</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -1859,6 +2324,11 @@
           <t>дождь</t>
         </is>
       </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>дождь</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -1883,6 +2353,21 @@
       <c r="I51" t="inlineStr">
         <is>
           <t>элемент, юань</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>юань (денежная единица Китая); элемент (в составе 元素)</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>для денег (十元钱)</t>
+        </is>
+      </c>
+      <c r="X51" t="inlineStr">
+        <is>
+          <t>значение «элемент» только в составе слова 元素</t>
         </is>
       </c>
     </row>
